--- a/feedback_forms/003_feedback_on_future_initiatives--feedback_forms.xlsx
+++ b/feedback_forms/003_feedback_on_future_initiatives--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>proposed_programs</t>
+          <t>proposed_programs_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Proposed Programs</t>
+          <t>Proposed Programs 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>comparison_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Comparison 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>roadmap</t>
+          <t>roadmap_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Roadmap</t>
+          <t>Roadmap 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -712,7 +712,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>roadmap</t>
+          <t>roadmap_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -764,7 +764,7 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
@@ -823,7 +823,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>proposed_programs_choices</t>
+          <t>proposed_programs_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -840,7 +840,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>proposed_programs_choices</t>
+          <t>proposed_programs_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -942,7 +942,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>comparison_choices</t>
+          <t>comparison_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>comparison_choices</t>
+          <t>comparison_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -976,51 +976,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>roadmap_choices</t>
+          <t>roadmap_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>roadmap_choices</t>
+          <t>roadmap_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>roadmap_choices</t>
+          <t>roadmap_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
